--- a/data/csv/建筑与工人系统/防御塔/全部箭塔成长路线_分路线录像提取V1.0.xlsx
+++ b/data/csv/建筑与工人系统/防御塔/全部箭塔成长路线_分路线录像提取V1.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26970" windowHeight="17550" activeTab="3"/>
+    <workbookView windowWidth="29820" windowHeight="12765" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="路线总览" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="411">
   <si>
     <t>全部箭塔成长路线：分路线录像提取总览</t>
   </si>
@@ -369,10 +369,70 @@
     <t>N</t>
   </si>
   <si>
-    <t>死亡之塔LV1</t>
-  </si>
-  <si>
-    <t>致命一击Lv1：13%概率造成5倍暴击</t>
+    <r>
+      <t>死亡之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>LV1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>致命一击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>13%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>概率造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍暴击</t>
+    </r>
   </si>
   <si>
     <t>N阶段转职；人口+1</t>
@@ -390,7 +450,57 @@
     <t>死亡之塔LV2</t>
   </si>
   <si>
-    <t>致命一击Lv2：16%概率造成5倍暴击</t>
+    <r>
+      <t>致命一击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>概率造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍暴击</t>
+    </r>
   </si>
   <si>
     <t>死亡之塔LV3</t>
@@ -408,13 +518,73 @@
     <t>死亡之塔LV5</t>
   </si>
   <si>
-    <t>致命一击Lv5：22%概率造成5倍暴击</t>
+    <r>
+      <t>致命一击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>22%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>概率造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍暴击</t>
+    </r>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>碎骨重炮LV1</t>
+    <r>
+      <t>碎骨重炮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>LV1</t>
+    </r>
   </si>
   <si>
     <t>致命一击Lv5：22%/5倍
@@ -434,8 +604,106 @@
     <t>碎骨重炮LV3</t>
   </si>
   <si>
-    <t>致命一击Lv5：22%/5倍
-碎骨重炮Lv3：每攻击7次，下一击必定10倍暴击</t>
+    <r>
+      <t>致命一击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>22%/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碎骨重炮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：每攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次，下一击必定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍暴击</t>
+    </r>
   </si>
   <si>
     <t>碎骨重炮LV4</t>
@@ -445,11 +713,119 @@
 碎骨重炮Lv4：每攻击6次，下一击必定10倍暴击</t>
   </si>
   <si>
-    <t>碎骨重炮LV5</t>
-  </si>
-  <si>
-    <t>致命一击Lv5：22%/5倍
-碎骨重炮Lv5：每攻击6次，下一击必定10倍暴击</t>
+    <r>
+      <t>碎骨重炮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>LV5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>致命一击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>22%/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碎骨重炮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：每攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次，下一击必定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍暴击</t>
+    </r>
   </si>
   <si>
     <t>SR</t>
@@ -469,34 +845,23 @@
     <t>死神榴弹炮LV2</t>
   </si>
   <si>
-    <t>死神榴弹炮LV3</t>
+    <r>
+      <t>死神榴弹炮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>LV3</t>
+    </r>
   </si>
   <si>
     <t>死神榴弹炮LV4</t>
   </si>
   <si>
     <t>死神榴弹炮LV5</t>
-  </si>
-  <si>
-    <t>SSR</t>
-  </si>
-  <si>
-    <t>死神榴弹炮LV6</t>
-  </si>
-  <si>
-    <t>最终塔LV6开始稀有度前缀变为SSR</t>
-  </si>
-  <si>
-    <t>死神榴弹炮LV7</t>
-  </si>
-  <si>
-    <t>死神榴弹炮LV8</t>
-  </si>
-  <si>
-    <t>死神榴弹炮LV9</t>
-  </si>
-  <si>
-    <t>死神榴弹炮LV10</t>
   </si>
   <si>
     <r>
@@ -658,6 +1023,191 @@
     </r>
   </si>
   <si>
+    <t>SSR</t>
+  </si>
+  <si>
+    <t>死神榴弹炮LV6</t>
+  </si>
+  <si>
+    <t>最终塔LV6开始稀有度前缀变为SSR</t>
+  </si>
+  <si>
+    <t>死神榴弹炮LV7</t>
+  </si>
+  <si>
+    <t>死神榴弹炮LV8</t>
+  </si>
+  <si>
+    <t>死神榴弹炮LV9</t>
+  </si>
+  <si>
+    <t>死神榴弹炮LV10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>致命一击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>22%/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碎骨重炮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：每攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次，下一击必定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>倍暴击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>死神榴弹炮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：暴击时对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>码范围造成该次暴击伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>200%</t>
+    </r>
+  </si>
+  <si>
     <t>本路线累计成本（箭塔1-1 → 最终塔LV10）</t>
   </si>
   <si>
@@ -698,6 +1248,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>激光</t>
     </r>
     <r>
@@ -762,6 +1317,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>激光</t>
     </r>
     <r>
@@ -943,7 +1503,65 @@
     <t>闪电塔LV1</t>
   </si>
   <si>
-    <t>闪电打击Lv1：弹射4个敌人；100%攻击力；每次弹射衰减10%</t>
+    <r>
+      <t>闪电打击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：弹射</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个敌人；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力；每次弹射衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10%</t>
+    </r>
   </si>
   <si>
     <t>闪电塔LV2</t>
@@ -967,7 +1585,65 @@
     <t>闪电塔LV5</t>
   </si>
   <si>
-    <t>闪电打击Lv5：弹射7个敌人；100%攻击力；每次弹射衰减10%</t>
+    <r>
+      <t>闪电打击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：弹射</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个敌人；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力；每次弹射衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10%</t>
+    </r>
   </si>
   <si>
     <t>闪电魔塔LV1</t>
@@ -987,8 +1663,90 @@
     <t>闪电魔塔LV3</t>
   </si>
   <si>
-    <t>闪电打击Lv5：弹射7个
-闪电魔塔Lv3：击杀生成雷电风暴区域；文本显示每1秒落雷</t>
+    <r>
+      <t>闪电打击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：弹射</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闪电魔塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：击杀生成雷电风暴区域；文本显示每</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>秒落雷</t>
+    </r>
   </si>
   <si>
     <t>闪电魔塔LV4</t>
@@ -1001,8 +1759,90 @@
     <t>闪电魔塔LV5</t>
   </si>
   <si>
-    <t>闪电打击Lv5：弹射7个
-闪电魔塔Lv5：击杀生成雷电风暴区域；文本显示每1秒落雷</t>
+    <r>
+      <t>闪电打击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：弹射</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闪电魔塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：击杀生成雷电风暴区域；文本显示每</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>秒落雷</t>
+    </r>
   </si>
   <si>
     <t>雷电扩散LV1</t>
@@ -1031,6 +1871,165 @@
     <t>雷电扩散LV7</t>
   </si>
   <si>
+    <r>
+      <t>闪电打击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：弹射</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个；每次衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">10%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闪电魔塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：击杀生成雷电风暴区域，每</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>秒落雷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>雷电扩散</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：落雷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>几率扩散，对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>码范围造成该次伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>200%</t>
+    </r>
+  </si>
+  <si>
     <t>雷电扩散LV8</t>
   </si>
   <si>
@@ -1345,7 +2344,49 @@
     <t>冰霜之塔LV1</t>
   </si>
   <si>
-    <t>冰霜攻击Lv1：100码范围攻击；减速25%</t>
+    <r>
+      <t>冰霜攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>码范围攻击；减速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25%</t>
+    </r>
   </si>
   <si>
     <t>半径400码范围敌人降低20%攻击速度</t>
@@ -1375,14 +2416,170 @@
     <t>冰霜之塔LV5</t>
   </si>
   <si>
-    <t>冰霜攻击Lv5：250码范围攻击；减速25%</t>
+    <r>
+      <t>冰霜攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>250</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>码范围攻击；减速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25%</t>
+    </r>
   </si>
   <si>
     <t>寒冰尖塔LV1</t>
   </si>
   <si>
-    <t>冰霜攻击Lv5：250码/减速25%
-寒冰尖塔Lv1：10%几率触发大范围暴风雪；每秒100%攻击力伤害并减速</t>
+    <r>
+      <t>冰霜攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>250</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>减速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">25%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寒冰尖塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>几率触发大范围暴风雪；每秒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力伤害并减速</t>
+    </r>
   </si>
   <si>
     <t>寒冰尖塔LV2</t>
@@ -1427,7 +2624,176 @@
     <t>极地方尖碑LV3</t>
   </si>
   <si>
-    <t>极地方尖碑LV4</t>
+    <r>
+      <t>极地方尖碑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>LV4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>冰霜攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>250</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>码范围攻击、减速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">25%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寒冰尖塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>几率触发暴风雪，每秒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力伤害并减速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>极地方尖碑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lv1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：半径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>码范围敌人攻击速度降低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20%</t>
+    </r>
   </si>
   <si>
     <t>极地方尖碑LV5</t>
@@ -2203,7 +3569,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2352,7 +3718,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2432,14 +3798,26 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2453,23 +3831,20 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2923,28 +4298,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8">
-      <c r="A1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:8">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
     </row>
     <row r="4" ht="15" spans="1:8">
       <c r="A4" s="3" t="s">
@@ -3155,86 +4530,86 @@
       </c>
     </row>
     <row r="14" ht="15" spans="1:8">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
     </row>
     <row r="15" ht="15" spans="1:8">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
     </row>
     <row r="16" ht="15" spans="1:8">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
     </row>
     <row r="17" ht="15" spans="1:8">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3279,22 +4654,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:22">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
@@ -3357,15 +4732,15 @@
       <c r="N4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="38" t="s">
+      <c r="P4" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="42"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:22">
       <c r="A5" s="5">
@@ -3716,7 +5091,7 @@
       <c r="C10" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="38" t="s">
         <v>111</v>
       </c>
       <c r="E10" s="12">
@@ -3743,7 +5118,7 @@
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="27" t="s">
         <v>112</v>
       </c>
       <c r="M10" s="13" t="s">
@@ -3811,7 +5186,7 @@
         <f t="shared" si="2"/>
         <v>3400</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="27" t="s">
         <v>118</v>
       </c>
       <c r="M11" s="13" t="s">
@@ -3952,7 +5327,7 @@
         <f t="shared" si="2"/>
         <v>10900</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="27" t="s">
         <v>124</v>
       </c>
       <c r="M14" s="13" t="s">
@@ -3972,7 +5347,7 @@
       <c r="C15" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="28" t="s">
         <v>126</v>
       </c>
       <c r="E15" s="15">
@@ -4093,7 +5468,7 @@
         <f t="shared" si="2"/>
         <v>130900</v>
       </c>
-      <c r="L17" s="16" t="s">
+      <c r="L17" s="29" t="s">
         <v>132</v>
       </c>
       <c r="M17" s="16" t="s">
@@ -4160,7 +5535,7 @@
       <c r="C19" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="28" t="s">
         <v>135</v>
       </c>
       <c r="E19" s="15">
@@ -4187,7 +5562,7 @@
         <f t="shared" si="2"/>
         <v>330900</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="L19" s="29" t="s">
         <v>136</v>
       </c>
       <c r="M19" s="16" t="s">
@@ -4301,7 +5676,7 @@
       <c r="C22" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="30" t="s">
         <v>142</v>
       </c>
       <c r="E22" s="18">
@@ -4422,8 +5797,8 @@
         <f t="shared" si="2"/>
         <v>1330900</v>
       </c>
-      <c r="L24" s="19" t="s">
-        <v>139</v>
+      <c r="L24" s="31" t="s">
+        <v>145</v>
       </c>
       <c r="M24" s="19" t="s">
         <v>16</v>
@@ -4440,10 +5815,10 @@
         <v>13</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E25" s="18">
         <v>2008101</v>
@@ -4476,7 +5851,7 @@
         <v>16</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" ht="42.75" spans="1:14">
@@ -4487,10 +5862,10 @@
         <v>13</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E26" s="18">
         <v>3008101</v>
@@ -4534,10 +5909,10 @@
         <v>13</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E27" s="18">
         <v>4008101</v>
@@ -4581,10 +5956,10 @@
         <v>13</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E28" s="18">
         <v>5008101</v>
@@ -4628,10 +6003,10 @@
         <v>13</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E29" s="18">
         <v>6008101</v>
@@ -4657,8 +6032,8 @@
         <f t="shared" si="2"/>
         <v>4330900</v>
       </c>
-      <c r="L29" s="39" t="s">
-        <v>152</v>
+      <c r="L29" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="M29" s="19" t="s">
         <v>16</v>
@@ -4669,7 +6044,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:14">
       <c r="A31" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -4689,7 +6064,7 @@
         <v>4</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
@@ -4697,13 +6072,13 @@
       <c r="N31" s="20"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:7">
-      <c r="A34" s="38"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
     </row>
     <row r="35" ht="15" spans="1:7">
       <c r="A35" s="22"/>
@@ -4800,26 +6175,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:22">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4878,15 +6253,15 @@
       <c r="N4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="35" t="s">
+      <c r="P4" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:22">
       <c r="A5" s="5">
@@ -5005,7 +6380,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R6" s="9" t="s">
         <v>98</v>
@@ -5014,13 +6389,13 @@
         <v>99</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -5082,13 +6457,13 @@
         <v>99</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -5150,10 +6525,10 @@
         <v>114</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>102</v>
@@ -5217,7 +6592,7 @@
         <v>110</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E10" s="12">
         <v>901</v>
@@ -5243,8 +6618,8 @@
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="L10" s="36" t="s">
-        <v>166</v>
+      <c r="L10" s="27" t="s">
+        <v>167</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>23</v>
@@ -5264,7 +6639,7 @@
         <v>110</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E11" s="12">
         <v>1501</v>
@@ -5290,8 +6665,8 @@
         <f t="shared" si="2"/>
         <v>3400</v>
       </c>
-      <c r="L11" s="36" t="s">
-        <v>168</v>
+      <c r="L11" s="27" t="s">
+        <v>169</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>23</v>
@@ -5311,7 +6686,7 @@
         <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E12" s="12">
         <v>2101</v>
@@ -5338,7 +6713,7 @@
         <v>5400</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>23</v>
@@ -5358,7 +6733,7 @@
         <v>110</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E13" s="12">
         <v>3901</v>
@@ -5385,7 +6760,7 @@
         <v>7900</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>23</v>
@@ -5405,7 +6780,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E14" s="12">
         <v>6101</v>
@@ -5432,7 +6807,7 @@
         <v>10900</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>23</v>
@@ -5452,7 +6827,7 @@
         <v>125</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E15" s="15">
         <v>12101</v>
@@ -5479,7 +6854,7 @@
         <v>30900</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>23</v>
@@ -5499,7 +6874,7 @@
         <v>125</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E16" s="15">
         <v>35101</v>
@@ -5526,7 +6901,7 @@
         <v>70900</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>23</v>
@@ -5546,7 +6921,7 @@
         <v>125</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E17" s="15">
         <v>50101</v>
@@ -5573,7 +6948,7 @@
         <v>130900</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>23</v>
@@ -5593,7 +6968,7 @@
         <v>125</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E18" s="15">
         <v>75101</v>
@@ -5620,7 +6995,7 @@
         <v>230900</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>23</v>
@@ -5640,7 +7015,7 @@
         <v>125</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E19" s="15">
         <v>108101</v>
@@ -5667,7 +7042,7 @@
         <v>330900</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>23</v>
@@ -5687,7 +7062,7 @@
         <v>137</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" s="18">
         <v>308101</v>
@@ -5714,7 +7089,7 @@
         <v>530900</v>
       </c>
       <c r="L20" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M20" s="19" t="s">
         <v>23</v>
@@ -5734,7 +7109,7 @@
         <v>137</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E21" s="18">
         <v>508101</v>
@@ -5761,7 +7136,7 @@
         <v>730900</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>23</v>
@@ -5781,7 +7156,7 @@
         <v>137</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E22" s="18">
         <v>808101</v>
@@ -5808,7 +7183,7 @@
         <v>930900</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M22" s="19" t="s">
         <v>23</v>
@@ -5828,7 +7203,7 @@
         <v>137</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E23" s="18">
         <v>1008101</v>
@@ -5855,7 +7230,7 @@
         <v>1130900</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M23" s="19" t="s">
         <v>23</v>
@@ -5875,7 +7250,7 @@
         <v>137</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E24" s="18">
         <v>1508101</v>
@@ -5902,7 +7277,7 @@
         <v>1330900</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M24" s="19" t="s">
         <v>23</v>
@@ -5919,10 +7294,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E25" s="18">
         <v>2008101</v>
@@ -5949,13 +7324,13 @@
         <v>1730900</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M25" s="19" t="s">
         <v>23</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" ht="42.75" spans="1:14">
@@ -5966,10 +7341,10 @@
         <v>20</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E26" s="18">
         <v>3008101</v>
@@ -5996,7 +7371,7 @@
         <v>2230900</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M26" s="19" t="s">
         <v>23</v>
@@ -6013,10 +7388,10 @@
         <v>20</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E27" s="18">
         <v>4008101</v>
@@ -6043,7 +7418,7 @@
         <v>2830900</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M27" s="19" t="s">
         <v>23</v>
@@ -6060,10 +7435,10 @@
         <v>20</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E28" s="18">
         <v>5008101</v>
@@ -6090,7 +7465,7 @@
         <v>3530900</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>23</v>
@@ -6107,10 +7482,10 @@
         <v>20</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E29" s="18">
         <v>6008101</v>
@@ -6137,7 +7512,7 @@
         <v>4330900</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M29" s="19" t="s">
         <v>23</v>
@@ -6148,7 +7523,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:14">
       <c r="A31" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -6168,7 +7543,7 @@
         <v>4</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
@@ -6176,13 +7551,13 @@
       <c r="N31" s="20"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:7">
-      <c r="A34" s="35"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
+      <c r="A34" s="40"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
     </row>
     <row r="35" ht="15" spans="1:7">
       <c r="A35" s="22"/>
@@ -6261,26 +7636,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:22">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6339,15 +7714,15 @@
       <c r="N4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="33" t="s">
+      <c r="P4" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="37"/>
+      <c r="U4" s="37"/>
+      <c r="V4" s="37"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:22">
       <c r="A5" s="5">
@@ -6466,7 +7841,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="R6" s="9" t="s">
         <v>98</v>
@@ -6475,13 +7850,13 @@
         <v>99</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" ht="27.75" spans="1:22">
@@ -6543,13 +7918,13 @@
         <v>99</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -6611,10 +7986,10 @@
         <v>114</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>102</v>
@@ -6671,14 +8046,14 @@
       <c r="A10" s="11">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="38" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>110</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E10" s="12">
         <v>901</v>
@@ -6704,8 +8079,8 @@
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>207</v>
+      <c r="L10" s="27" t="s">
+        <v>208</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>29</v>
@@ -6725,7 +8100,7 @@
         <v>110</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E11" s="12">
         <v>1501</v>
@@ -6752,7 +8127,7 @@
         <v>3400</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>29</v>
@@ -6772,7 +8147,7 @@
         <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E12" s="12">
         <v>2101</v>
@@ -6799,7 +8174,7 @@
         <v>5400</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>29</v>
@@ -6819,7 +8194,7 @@
         <v>110</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E13" s="12">
         <v>3901</v>
@@ -6846,7 +8221,7 @@
         <v>7900</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>29</v>
@@ -6866,7 +8241,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E14" s="12">
         <v>6101</v>
@@ -6892,8 +8267,8 @@
         <f t="shared" si="2"/>
         <v>10900</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>215</v>
+      <c r="L14" s="27" t="s">
+        <v>216</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>29</v>
@@ -6906,14 +8281,14 @@
       <c r="A15" s="14">
         <v>11</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="28" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>125</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E15" s="15">
         <v>12101</v>
@@ -6940,7 +8315,7 @@
         <v>30900</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>29</v>
@@ -6960,7 +8335,7 @@
         <v>125</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E16" s="15">
         <v>35101</v>
@@ -6987,7 +8362,7 @@
         <v>70900</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>29</v>
@@ -7007,7 +8382,7 @@
         <v>125</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E17" s="15">
         <v>50101</v>
@@ -7033,8 +8408,8 @@
         <f t="shared" si="2"/>
         <v>130900</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>221</v>
+      <c r="L17" s="29" t="s">
+        <v>222</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>29</v>
@@ -7054,7 +8429,7 @@
         <v>125</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E18" s="15">
         <v>75101</v>
@@ -7081,7 +8456,7 @@
         <v>230900</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>29</v>
@@ -7101,7 +8476,7 @@
         <v>125</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E19" s="15">
         <v>108101</v>
@@ -7127,8 +8502,8 @@
         <f t="shared" si="2"/>
         <v>330900</v>
       </c>
-      <c r="L19" s="16" t="s">
-        <v>225</v>
+      <c r="L19" s="29" t="s">
+        <v>226</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>29</v>
@@ -7148,7 +8523,7 @@
         <v>137</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E20" s="18">
         <v>308101</v>
@@ -7175,7 +8550,7 @@
         <v>530900</v>
       </c>
       <c r="L20" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M20" s="19" t="s">
         <v>29</v>
@@ -7195,7 +8570,7 @@
         <v>137</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E21" s="18">
         <v>508101</v>
@@ -7222,7 +8597,7 @@
         <v>730900</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>29</v>
@@ -7242,7 +8617,7 @@
         <v>137</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E22" s="18">
         <v>808101</v>
@@ -7269,7 +8644,7 @@
         <v>930900</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M22" s="19" t="s">
         <v>29</v>
@@ -7289,7 +8664,7 @@
         <v>137</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E23" s="18">
         <v>1008101</v>
@@ -7316,7 +8691,7 @@
         <v>1130900</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M23" s="19" t="s">
         <v>29</v>
@@ -7329,14 +8704,14 @@
       <c r="A24" s="17">
         <v>20</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="30" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>137</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E24" s="18">
         <v>1508101</v>
@@ -7363,7 +8738,7 @@
         <v>1330900</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M24" s="19" t="s">
         <v>29</v>
@@ -7380,10 +8755,10 @@
         <v>27</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E25" s="18">
         <v>2008101</v>
@@ -7410,13 +8785,13 @@
         <v>1730900</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M25" s="19" t="s">
         <v>29</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" ht="42.75" spans="1:14">
@@ -7427,10 +8802,10 @@
         <v>27</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E26" s="18">
         <v>3008101</v>
@@ -7456,8 +8831,8 @@
         <f t="shared" si="2"/>
         <v>2230900</v>
       </c>
-      <c r="L26" s="19" t="s">
-        <v>227</v>
+      <c r="L26" s="31" t="s">
+        <v>235</v>
       </c>
       <c r="M26" s="19" t="s">
         <v>29</v>
@@ -7474,10 +8849,10 @@
         <v>27</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E27" s="18">
         <v>4008101</v>
@@ -7504,7 +8879,7 @@
         <v>2830900</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M27" s="19" t="s">
         <v>29</v>
@@ -7521,10 +8896,10 @@
         <v>27</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E28" s="18">
         <v>5008101</v>
@@ -7551,7 +8926,7 @@
         <v>3530900</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>29</v>
@@ -7568,10 +8943,10 @@
         <v>27</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E29" s="18">
         <v>6008101</v>
@@ -7598,7 +8973,7 @@
         <v>4330900</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M29" s="19" t="s">
         <v>29</v>
@@ -7609,7 +8984,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:14">
       <c r="A31" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -7629,7 +9004,7 @@
         <v>4</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
@@ -7637,13 +9012,13 @@
       <c r="N31" s="20"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:7">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
     </row>
     <row r="35" ht="15" spans="1:7">
       <c r="A35" s="22"/>
@@ -7722,26 +9097,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:22">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7800,15 +9175,15 @@
       <c r="N4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="31" t="s">
+      <c r="P4" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:22">
       <c r="A5" s="5">
@@ -7927,7 +9302,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R6" s="9" t="s">
         <v>98</v>
@@ -7936,13 +9311,13 @@
         <v>99</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -8004,13 +9379,13 @@
         <v>99</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" ht="27.75" spans="1:22">
@@ -8072,10 +9447,10 @@
         <v>114</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>102</v>
@@ -8139,7 +9514,7 @@
         <v>110</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E10" s="12">
         <v>901</v>
@@ -8166,7 +9541,7 @@
         <v>1900</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>35</v>
@@ -8186,7 +9561,7 @@
         <v>110</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E11" s="12">
         <v>1501</v>
@@ -8213,7 +9588,7 @@
         <v>3400</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>35</v>
@@ -8233,7 +9608,7 @@
         <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E12" s="12">
         <v>2101</v>
@@ -8260,7 +9635,7 @@
         <v>5400</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>35</v>
@@ -8280,7 +9655,7 @@
         <v>110</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E13" s="12">
         <v>3901</v>
@@ -8307,7 +9682,7 @@
         <v>7900</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>35</v>
@@ -8327,7 +9702,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E14" s="12">
         <v>6101</v>
@@ -8354,7 +9729,7 @@
         <v>10900</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>35</v>
@@ -8374,7 +9749,7 @@
         <v>125</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E15" s="15">
         <v>12101</v>
@@ -8401,7 +9776,7 @@
         <v>30900</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>35</v>
@@ -8421,7 +9796,7 @@
         <v>125</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E16" s="15">
         <v>35101</v>
@@ -8448,7 +9823,7 @@
         <v>70900</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>35</v>
@@ -8468,7 +9843,7 @@
         <v>125</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E17" s="15">
         <v>50101</v>
@@ -8495,7 +9870,7 @@
         <v>130900</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>35</v>
@@ -8515,7 +9890,7 @@
         <v>125</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E18" s="15">
         <v>75101</v>
@@ -8542,7 +9917,7 @@
         <v>230900</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>35</v>
@@ -8562,7 +9937,7 @@
         <v>125</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E19" s="15">
         <v>108101</v>
@@ -8589,7 +9964,7 @@
         <v>330900</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>35</v>
@@ -8609,7 +9984,7 @@
         <v>137</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E20" s="18">
         <v>308101</v>
@@ -8636,7 +10011,7 @@
         <v>530900</v>
       </c>
       <c r="L20" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M20" s="19" t="s">
         <v>35</v>
@@ -8656,7 +10031,7 @@
         <v>137</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E21" s="18">
         <v>508101</v>
@@ -8683,7 +10058,7 @@
         <v>730900</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>35</v>
@@ -8703,7 +10078,7 @@
         <v>137</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E22" s="18">
         <v>808101</v>
@@ -8730,7 +10105,7 @@
         <v>930900</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M22" s="19" t="s">
         <v>35</v>
@@ -8750,7 +10125,7 @@
         <v>137</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E23" s="18">
         <v>1008101</v>
@@ -8777,7 +10152,7 @@
         <v>1130900</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M23" s="19" t="s">
         <v>35</v>
@@ -8797,7 +10172,7 @@
         <v>137</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E24" s="18">
         <v>1508101</v>
@@ -8824,7 +10199,7 @@
         <v>1330900</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M24" s="19" t="s">
         <v>35</v>
@@ -8841,10 +10216,10 @@
         <v>33</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E25" s="18">
         <v>2008101</v>
@@ -8871,13 +10246,13 @@
         <v>1730900</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M25" s="19" t="s">
         <v>35</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" ht="57" spans="1:14">
@@ -8888,10 +10263,10 @@
         <v>33</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E26" s="18">
         <v>3008101</v>
@@ -8918,7 +10293,7 @@
         <v>2230900</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M26" s="19" t="s">
         <v>35</v>
@@ -8935,10 +10310,10 @@
         <v>33</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E27" s="18">
         <v>4008101</v>
@@ -8965,7 +10340,7 @@
         <v>2830900</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M27" s="19" t="s">
         <v>35</v>
@@ -8982,10 +10357,10 @@
         <v>33</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E28" s="18">
         <v>5008101</v>
@@ -9012,7 +10387,7 @@
         <v>3530900</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>35</v>
@@ -9029,10 +10404,10 @@
         <v>33</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E29" s="18">
         <v>6008101</v>
@@ -9059,7 +10434,7 @@
         <v>4330900</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M29" s="19" t="s">
         <v>35</v>
@@ -9070,7 +10445,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:14">
       <c r="A31" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -9090,7 +10465,7 @@
         <v>4</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
@@ -9098,13 +10473,13 @@
       <c r="N31" s="20"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:7">
-      <c r="A34" s="31"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
     </row>
     <row r="35" ht="15" spans="1:7">
       <c r="A35" s="22"/>
@@ -9183,26 +10558,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:22">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9261,15 +10636,15 @@
       <c r="N4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="28" t="s">
+      <c r="P4" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:22">
       <c r="A5" s="5">
@@ -9388,7 +10763,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="R6" s="9" t="s">
         <v>98</v>
@@ -9397,13 +10772,13 @@
         <v>99</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -9465,13 +10840,13 @@
         <v>99</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -9533,10 +10908,10 @@
         <v>114</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>102</v>
@@ -9600,7 +10975,7 @@
         <v>110</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E10" s="12">
         <v>901</v>
@@ -9627,7 +11002,7 @@
         <v>1900</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>41</v>
@@ -9647,7 +11022,7 @@
         <v>110</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E11" s="12">
         <v>1501</v>
@@ -9674,7 +11049,7 @@
         <v>3400</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>41</v>
@@ -9694,7 +11069,7 @@
         <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E12" s="12">
         <v>2101</v>
@@ -9721,7 +11096,7 @@
         <v>5400</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>41</v>
@@ -9741,7 +11116,7 @@
         <v>110</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E13" s="12">
         <v>3901</v>
@@ -9768,7 +11143,7 @@
         <v>7900</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>41</v>
@@ -9788,7 +11163,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E14" s="12">
         <v>6101</v>
@@ -9815,7 +11190,7 @@
         <v>10900</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>41</v>
@@ -9835,7 +11210,7 @@
         <v>125</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E15" s="15">
         <v>12101</v>
@@ -9862,7 +11237,7 @@
         <v>30900</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>41</v>
@@ -9882,7 +11257,7 @@
         <v>125</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E16" s="15">
         <v>35101</v>
@@ -9909,7 +11284,7 @@
         <v>70900</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>41</v>
@@ -9929,7 +11304,7 @@
         <v>125</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E17" s="15">
         <v>50101</v>
@@ -9956,7 +11331,7 @@
         <v>130900</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>41</v>
@@ -9976,7 +11351,7 @@
         <v>125</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E18" s="15">
         <v>75101</v>
@@ -10003,7 +11378,7 @@
         <v>230900</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>41</v>
@@ -10023,7 +11398,7 @@
         <v>125</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E19" s="15">
         <v>108101</v>
@@ -10050,7 +11425,7 @@
         <v>330900</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>41</v>
@@ -10063,14 +11438,14 @@
       <c r="A20" s="17">
         <v>16</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="30" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>137</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E20" s="18">
         <v>308101</v>
@@ -10097,7 +11472,7 @@
         <v>530900</v>
       </c>
       <c r="L20" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M20" s="19" t="s">
         <v>41</v>
@@ -10117,7 +11492,7 @@
         <v>137</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E21" s="18">
         <v>508101</v>
@@ -10144,7 +11519,7 @@
         <v>730900</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>41</v>
@@ -10164,7 +11539,7 @@
         <v>137</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E22" s="18">
         <v>808101</v>
@@ -10191,7 +11566,7 @@
         <v>930900</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M22" s="19" t="s">
         <v>41</v>
@@ -10211,7 +11586,7 @@
         <v>137</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E23" s="18">
         <v>1008101</v>
@@ -10238,7 +11613,7 @@
         <v>1130900</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M23" s="19" t="s">
         <v>41</v>
@@ -10258,7 +11633,7 @@
         <v>137</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E24" s="18">
         <v>1508101</v>
@@ -10285,7 +11660,7 @@
         <v>1330900</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M24" s="19" t="s">
         <v>41</v>
@@ -10302,10 +11677,10 @@
         <v>39</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E25" s="18">
         <v>2008101</v>
@@ -10332,13 +11707,13 @@
         <v>1730900</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M25" s="19" t="s">
         <v>41</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" ht="42.75" spans="1:14">
@@ -10349,10 +11724,10 @@
         <v>39</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E26" s="18">
         <v>3008101</v>
@@ -10379,7 +11754,7 @@
         <v>2230900</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M26" s="19" t="s">
         <v>41</v>
@@ -10396,10 +11771,10 @@
         <v>39</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E27" s="18">
         <v>4008101</v>
@@ -10426,7 +11801,7 @@
         <v>2830900</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M27" s="19" t="s">
         <v>41</v>
@@ -10443,10 +11818,10 @@
         <v>39</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E28" s="18">
         <v>5008101</v>
@@ -10473,7 +11848,7 @@
         <v>3530900</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>41</v>
@@ -10490,10 +11865,10 @@
         <v>39</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E29" s="18">
         <v>6008101</v>
@@ -10520,7 +11895,7 @@
         <v>4330900</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M29" s="19" t="s">
         <v>41</v>
@@ -10531,7 +11906,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:14">
       <c r="A31" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -10551,7 +11926,7 @@
         <v>4</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
@@ -10559,13 +11934,13 @@
       <c r="N31" s="20"/>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:7">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
     </row>
     <row r="35" ht="15" spans="1:7">
       <c r="A35" s="22"/>
@@ -10663,7 +12038,7 @@
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10849,22 +12224,22 @@
         <v>4</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R6" s="9" t="s">
         <v>92</v>
       </c>
       <c r="S6" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -10917,7 +12292,7 @@
         <v>4</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R7" s="10" t="s">
         <v>98</v>
@@ -10926,13 +12301,13 @@
         <v>99</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -10994,10 +12369,10 @@
         <v>93</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>96</v>
@@ -11062,13 +12437,13 @@
         <v>99</v>
       </c>
       <c r="T9" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="V9" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -11082,7 +12457,7 @@
         <v>110</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E10" s="12">
         <v>901</v>
@@ -11108,8 +12483,8 @@
         <f t="shared" si="2"/>
         <v>1900</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>334</v>
+      <c r="L10" s="27" t="s">
+        <v>336</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>47</v>
@@ -11130,10 +12505,10 @@
         <v>114</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="V10" s="9" t="s">
         <v>102</v>
@@ -11150,7 +12525,7 @@
         <v>110</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E11" s="12">
         <v>1501</v>
@@ -11177,7 +12552,7 @@
         <v>3400</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>47</v>
@@ -11197,7 +12572,7 @@
         <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E12" s="12">
         <v>2101</v>
@@ -11224,7 +12599,7 @@
         <v>5400</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>47</v>
@@ -11244,7 +12619,7 @@
         <v>110</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E13" s="12">
         <v>3901</v>
@@ -11271,7 +12646,7 @@
         <v>7900</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>47</v>
@@ -11291,7 +12666,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E14" s="12">
         <v>6101</v>
@@ -11317,8 +12692,8 @@
         <f t="shared" si="2"/>
         <v>10900</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>344</v>
+      <c r="L14" s="27" t="s">
+        <v>346</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>47</v>
@@ -11331,14 +12706,14 @@
       <c r="A15" s="14">
         <v>11</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="28" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>125</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E15" s="15">
         <v>12101</v>
@@ -11364,8 +12739,8 @@
         <f t="shared" si="2"/>
         <v>30900</v>
       </c>
-      <c r="L15" s="16" t="s">
-        <v>346</v>
+      <c r="L15" s="29" t="s">
+        <v>348</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>47</v>
@@ -11385,7 +12760,7 @@
         <v>125</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E16" s="15">
         <v>35101</v>
@@ -11412,7 +12787,7 @@
         <v>70900</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>47</v>
@@ -11432,7 +12807,7 @@
         <v>125</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E17" s="15">
         <v>50101</v>
@@ -11459,7 +12834,7 @@
         <v>130900</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>47</v>
@@ -11479,7 +12854,7 @@
         <v>125</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E18" s="15">
         <v>75101</v>
@@ -11506,7 +12881,7 @@
         <v>230900</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>47</v>
@@ -11526,7 +12901,7 @@
         <v>125</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E19" s="15">
         <v>108101</v>
@@ -11553,7 +12928,7 @@
         <v>330900</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>47</v>
@@ -11573,7 +12948,7 @@
         <v>137</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E20" s="18">
         <v>308101</v>
@@ -11600,7 +12975,7 @@
         <v>530900</v>
       </c>
       <c r="L20" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M20" s="19" t="s">
         <v>47</v>
@@ -11620,7 +12995,7 @@
         <v>137</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E21" s="18">
         <v>508101</v>
@@ -11647,7 +13022,7 @@
         <v>730900</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>47</v>
@@ -11667,7 +13042,7 @@
         <v>137</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E22" s="18">
         <v>808101</v>
@@ -11694,7 +13069,7 @@
         <v>930900</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M22" s="19" t="s">
         <v>47</v>
@@ -11713,8 +13088,8 @@
       <c r="C23" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>359</v>
+      <c r="D23" s="30" t="s">
+        <v>361</v>
       </c>
       <c r="E23" s="18">
         <v>1008101</v>
@@ -11740,8 +13115,8 @@
         <f t="shared" si="2"/>
         <v>1130900</v>
       </c>
-      <c r="L23" s="19" t="s">
-        <v>356</v>
+      <c r="L23" s="31" t="s">
+        <v>362</v>
       </c>
       <c r="M23" s="19" t="s">
         <v>47</v>
@@ -11761,7 +13136,7 @@
         <v>137</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E24" s="18">
         <v>1508101</v>
@@ -11788,7 +13163,7 @@
         <v>1330900</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M24" s="19" t="s">
         <v>47</v>
@@ -11805,10 +13180,10 @@
         <v>45</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E25" s="18">
         <v>2008101</v>
@@ -11835,13 +13210,13 @@
         <v>1730900</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M25" s="19" t="s">
         <v>47</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" ht="42.75" spans="1:14">
@@ -11852,10 +13227,10 @@
         <v>45</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E26" s="18">
         <v>3008101</v>
@@ -11882,7 +13257,7 @@
         <v>2230900</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M26" s="19" t="s">
         <v>47</v>
@@ -11899,10 +13274,10 @@
         <v>45</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E27" s="18">
         <v>4008101</v>
@@ -11929,7 +13304,7 @@
         <v>2830900</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M27" s="19" t="s">
         <v>47</v>
@@ -11946,10 +13321,10 @@
         <v>45</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E28" s="18">
         <v>5008101</v>
@@ -11976,7 +13351,7 @@
         <v>3530900</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>47</v>
@@ -11993,10 +13368,10 @@
         <v>45</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E29" s="18">
         <v>6008101</v>
@@ -12023,7 +13398,7 @@
         <v>4330900</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M29" s="19" t="s">
         <v>47</v>
@@ -12034,7 +13409,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:14">
       <c r="A31" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -12054,7 +13429,7 @@
         <v>4</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
@@ -12184,7 +13559,7 @@
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12379,10 +13754,10 @@
         <v>93</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="V6" s="9" t="s">
         <v>96</v>
@@ -12447,13 +13822,13 @@
         <v>99</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -12515,10 +13890,10 @@
         <v>93</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>96</v>
@@ -12583,13 +13958,13 @@
         <v>99</v>
       </c>
       <c r="T9" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="V9" s="10" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -12603,7 +13978,7 @@
         <v>110</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E10" s="12">
         <v>901</v>
@@ -12630,7 +14005,7 @@
         <v>1900</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>53</v>
@@ -12651,10 +14026,10 @@
         <v>114</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="V10" s="9" t="s">
         <v>102</v>
@@ -12671,7 +14046,7 @@
         <v>110</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E11" s="12">
         <v>1501</v>
@@ -12698,7 +14073,7 @@
         <v>3400</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M11" s="13" t="s">
         <v>53</v>
@@ -12718,7 +14093,7 @@
         <v>110</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E12" s="12">
         <v>2101</v>
@@ -12745,7 +14120,7 @@
         <v>5400</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M12" s="13" t="s">
         <v>53</v>
@@ -12765,7 +14140,7 @@
         <v>110</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E13" s="12">
         <v>3901</v>
@@ -12792,7 +14167,7 @@
         <v>7900</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M13" s="13" t="s">
         <v>53</v>
@@ -12812,7 +14187,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E14" s="12">
         <v>6101</v>
@@ -12839,7 +14214,7 @@
         <v>10900</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>53</v>
@@ -12859,7 +14234,7 @@
         <v>125</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E15" s="15">
         <v>12101</v>
@@ -12886,7 +14261,7 @@
         <v>30900</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>53</v>
@@ -12906,7 +14281,7 @@
         <v>125</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E16" s="15">
         <v>35101</v>
@@ -12933,7 +14308,7 @@
         <v>70900</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>53</v>
@@ -12953,7 +14328,7 @@
         <v>125</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E17" s="15">
         <v>50101</v>
@@ -12980,7 +14355,7 @@
         <v>130900</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>53</v>
@@ -13000,7 +14375,7 @@
         <v>125</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E18" s="15">
         <v>75101</v>
@@ -13027,7 +14402,7 @@
         <v>230900</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>53</v>
@@ -13047,7 +14422,7 @@
         <v>125</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E19" s="15">
         <v>108101</v>
@@ -13074,7 +14449,7 @@
         <v>330900</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>53</v>
@@ -13094,7 +14469,7 @@
         <v>137</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E20" s="18">
         <v>308101</v>
@@ -13121,7 +14496,7 @@
         <v>530900</v>
       </c>
       <c r="L20" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M20" s="19" t="s">
         <v>53</v>
@@ -13141,7 +14516,7 @@
         <v>137</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E21" s="18">
         <v>508101</v>
@@ -13168,7 +14543,7 @@
         <v>730900</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>53</v>
@@ -13188,7 +14563,7 @@
         <v>137</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E22" s="18">
         <v>808101</v>
@@ -13215,7 +14590,7 @@
         <v>930900</v>
       </c>
       <c r="L22" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M22" s="19" t="s">
         <v>53</v>
@@ -13235,7 +14610,7 @@
         <v>137</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E23" s="18">
         <v>1008101</v>
@@ -13262,7 +14637,7 @@
         <v>1130900</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M23" s="19" t="s">
         <v>53</v>
@@ -13282,7 +14657,7 @@
         <v>137</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E24" s="18">
         <v>1508101</v>
@@ -13309,7 +14684,7 @@
         <v>1330900</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M24" s="19" t="s">
         <v>53</v>
@@ -13326,10 +14701,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E25" s="18">
         <v>2008101</v>
@@ -13356,13 +14731,13 @@
         <v>1730900</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M25" s="19" t="s">
         <v>53</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" ht="42.75" spans="1:14">
@@ -13373,10 +14748,10 @@
         <v>51</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E26" s="18">
         <v>3008101</v>
@@ -13403,7 +14778,7 @@
         <v>2230900</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M26" s="19" t="s">
         <v>53</v>
@@ -13420,10 +14795,10 @@
         <v>51</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E27" s="18">
         <v>4008101</v>
@@ -13450,7 +14825,7 @@
         <v>2830900</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M27" s="19" t="s">
         <v>53</v>
@@ -13467,10 +14842,10 @@
         <v>51</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E28" s="18">
         <v>5008101</v>
@@ -13497,7 +14872,7 @@
         <v>3530900</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>53</v>
@@ -13514,10 +14889,10 @@
         <v>51</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E29" s="18">
         <v>6008101</v>
@@ -13544,7 +14919,7 @@
         <v>4330900</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M29" s="19" t="s">
         <v>53</v>
@@ -13555,7 +14930,7 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:14">
       <c r="A31" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -13575,7 +14950,7 @@
         <v>4</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
